--- a/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
+++ b/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="124">
   <si>
     <t xml:space="preserve">פרויקט נווה יעקב – סיכום הכנסות, הוצאות ורווח</t>
   </si>
@@ -72,328 +72,328 @@
     <t xml:space="preserve">יבוא HPL – 3 מכולות</t>
   </si>
   <si>
+    <t xml:space="preserve">קונסטרוקציה / ברגים / ברקטים / פרופילים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הוצאות כלליות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הובלות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס ושונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📤 סה"כ הוצאות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ רווח הפרויקט עד היום</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לפי החוזה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חוזה: 2,400 מ"ר × 600 ₪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בפועל: 3,000 מ"ר × 600 ₪ (לפי הגיליון)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏳ יתרה לגבייה לפי 3,000 מ"ר (ללא גליפים)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לפני מע"מ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ שאלות פתוחות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מורט: בגיליון יש "סך הכל 10,089" (2,950$) ושורה נוספת של 3,409.28 (תואמת לתשלום של מטה ל-MURAT ב-05/10). כאן נספר רק 10,089, בהנחה שה-3,409.28 הוא חלק מהסכום הזה. אם זה תשלום נוסף - הרווח יורד ב-3,409.28.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גור את שיפר - חשבונית אחת בלי סכום ("?") - לא נספרה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גרייטדור הובלה 7,197 - מסומן "לקזז בסוף מחאדר". אם יקוזז מהתשלום לחאדר, ההוצאה לא משתנה (רק עוברת מקטגוריה לקטגוריה).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר - "מזומן לפני פסח" 95,000 הוא תשלום במזומן; שאר הסכומים לפי חשבוניות. בגיליון "הכנסות . הוצאות שאין שיוך" יש גם "סדין קאפ חיפ" 10,000 (18/03) + 6,520 (20/03) "תשלום חאדר בית ירושלמי" - לוודא שאינם תוספת ל-20,000 של סדין קאק.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גליפים (700 ₪ למטר) - אין נתון על כמות, לכן לא נכללו ביתרה לגבייה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בידוד מרפסת רוטנברג 99,716 - עבר דרכנו ובית ירושלמי החזיר, לכן לא נכלל (מופיע בנפרד בתחתית גיליון "הוצאות"). ⚠️ ההחזר מבית ירושלמי לא צריך להופיע ב-10 התקבולים - אם הוא נכלל שם, יש להוריד אותו מההכנסות.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בגיליון "סיכום" של הקובץ המקורי נווה יעקב עדיין מופיע עם נתונים ישנים: הכנסות 1,104,121 / הוצאות 725,687 / רווח 378,434.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פרויקט נווה יעקב – הכנסות (תקבולים מהמזמין)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מזמין: רימון בדאען ע"י בית ירושלמי · הסכומים לא כוללים מע"מ (כפי שבגיליון המקור; ×1.18 = הסכום שהתקבל בפועל)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תאריך</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סכום לפני מע"מ (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כולל מע"מ (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/02/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ תואם לבנק מטה 10/08: העברת זה"ב בית ירושלמי 112,968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ הכנסות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פרויקט נווה יעקב – הוצאות לפי קטגוריה (לא כולל מע"מ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קטגוריה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ספק / תיאור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סכום ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הערות / מקור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר – סדין קאק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר – מזומן לפני פסח</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מזומן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר (ראם משלוחים)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91013_invoice.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חאדר (משי ניהול עובדים)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נדב איטומים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הודעה מיום 28.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ קבלן מבצע – חאדר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכולה 1 – 384.61 מ"ר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipment 1 – Commercial Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכולה 2 – 991.25 מ"ר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipment 2 – Commercial Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מכולה 3 – 1,487.4 מ"ר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipment 3 – Commercial Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עלות מט"ח לפי 3 מכולות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ יבוא HPL – 3 מכולות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גור את שיפר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI266002349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI266003946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פרופילים DB (מילי סויסה)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅ תואם לבנק מטה 03/08: 10,761.60 כולל מע"מ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גור את שיפר – חשבונית נוספת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ סכום לא מולא בגיליון המקור ("?")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ קונסטרוקציה / ברגים / ברקטים / פרופילים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ברגים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הדפסת תוכניות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אלקטרו סליל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גאלה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ארפק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גאלה קלאסיק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גאלה קלאסיק – ברגים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ארפק די</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210012492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210012573 · העברה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רוטנברג – ספריי קצף</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210012671 · העברה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ הוצאות כלליות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גרייטדור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"לקזז בסוף מחאדר" – כשיקוזז, ההוצאה תעבור לחאדר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">משאית מגור את שיפר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הובלה מההשיקוף לפרויקט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">משלוח גור + ארפק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ביט · קרגו.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ הובלות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מורט – מהנדס (2,950 $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בגיליון המקור מופיעה גם שורה של 3,409.28 – ראה שאלות פתוחות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גרייטדור – התקנת מחיצה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice-2055.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ מהנדס ושונות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סה"כ הוצאות הפרויקט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💡 עבר דרכנו – לא נכלל בסיכום הפרויקט</t>
+  </si>
+  <si>
     <t xml:space="preserve">בידוד מרפסת – רוטנברג</t>
   </si>
   <si>
-    <t xml:space="preserve">קונסטרוקציה / ברגים / ברקטים / פרופילים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הוצאות כלליות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הובלות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס ושונות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📤 סה"כ הוצאות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ רווח הפרויקט עד היום</t>
-  </si>
-  <si>
-    <t xml:space="preserve">לפי החוזה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חוזה: 2,400 מ"ר × 600 ₪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בפועל: 3,000 מ"ר × 600 ₪ (לפי הגיליון)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⏳ יתרה לגבייה לפי 3,000 מ"ר (ללא גליפים)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">לפני מע"מ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ שאלות פתוחות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בידוד מרפסת רוטנברג 99,716 ₪ לא נכלל בסיכום בגיליון המקור - כאן הוא נספר כהוצאה של הפרויקט. בפועל ישר שילמה בצ׳קים 118,651 כולל מע"מ (≈100,551 לפני מע"מ) - פער של כ-835 ₪. חשבונית מס טרם התקבלה.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מורט: בגיליון יש "סך הכל 10,089" (2,950$) ושורה נוספת של 3,409.28 (תואמת לתשלום של מטה ל-MURAT ב-05/10). כאן נספר רק 10,089, בהנחה שה-3,409.28 הוא חלק מהסכום הזה. אם זה תשלום נוסף - הרווח יורד ב-3,409.28.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גור את שיפר - חשבונית אחת בלי סכום ("?") - לא נספרה.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גרייטדור הובלה 7,197 - מסומן "לקזז בסוף מחאדר". אם יקוזז מהתשלום לחאדר, ההוצאה לא משתנה (רק עוברת מקטגוריה לקטגוריה).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר - "מזומן לפני פסח" 95,000 הוא תשלום במזומן; שאר הסכומים לפי חשבוניות. בגיליון "הכנסות . הוצאות שאין שיוך" יש גם "סדין קאפ חיפ" 10,000 (18/03) + 6,520 (20/03) "תשלום חאדר בית ירושלמי" - לוודא שאינם תוספת ל-20,000 של סדין קאק.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גליפים (700 ₪ למטר) - אין נתון על כמות, לכן לא נכללו ביתרה לגבייה.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בגיליון "סיכום" של הקובץ המקורי נווה יעקב עדיין מופיע עם נתונים ישנים: הכנסות 1,104,121 / הוצאות 725,687 / רווח 378,434.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">פרויקט נווה יעקב – הכנסות (תקבולים מהמזמין)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מזמין: רימון בדאען ע"י בית ירושלמי · הסכומים לא כוללים מע"מ (כפי שבגיליון המקור; ×1.18 = הסכום שהתקבל בפועל)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תאריך</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סכום לפני מע"מ (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כולל מע"מ (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/02/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ תואם לבנק מטה 10/08: העברת זה"ב בית ירושלמי 112,968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ הכנסות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">פרויקט נווה יעקב – הוצאות לפי קטגוריה (לא כולל מע"מ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">קטגוריה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ספק / תיאור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סכום ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערות / מקור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר – סדין קאק</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר – מזומן לפני פסח</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מזומן</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר (ראם משלוחים)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91013_invoice.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חאדר (משי ניהול עובדים)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">נדב איטומים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הודעה מיום 28.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ קבלן מבצע – חאדר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכולה 1 – 384.61 מ"ר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipment 1 – Commercial Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכולה 2 – 991.25 מ"ר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipment 2 – Commercial Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מכולה 3 – 1,487.4 מ"ר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipment 3 – Commercial Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">עלות מט"ח לפי 3 מכולות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ יבוא HPL – 3 מכולות</t>
-  </si>
-  <si>
     <t xml:space="preserve">מ. רוטנברג ובניו – בידוד מרפסת</t>
   </si>
   <si>
     <t xml:space="preserve">06/07 + 26/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠️ לא נכלל בסיכום בגיליון המקור. שולם בצ׳קים של ישר (59,825 + 58,826 = 118,651 כולל מע"מ). חשבונית מס טרם התקבלה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ בידוד מרפסת – רוטנברג</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גור את שיפר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI266002349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI266003946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">פרופילים DB (מילי סויסה)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅ תואם לבנק מטה 03/08: 10,761.60 כולל מע"מ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גור את שיפר – חשבונית נוספת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️ סכום לא מולא בגיליון המקור ("?")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ קונסטרוקציה / ברגים / ברקטים / פרופילים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ברגים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הדפסת תוכניות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">אלקטרו סליל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גאלה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ארפק</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גאלה קלאסיק</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גאלה קלאסיק – ברגים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ארפק די</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210012492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210012573 · העברה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">רוטנברג – ספריי קצף</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210012671 · העברה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ הוצאות כלליות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גרייטדור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"לקזז בסוף מחאדר" – כשיקוזז, ההוצאה תעבור לחאדר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">משאית מגור את שיפר</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הובלה מההשיקוף לפרויקט</t>
-  </si>
-  <si>
-    <t xml:space="preserve">משלוח גור + ארפק</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ביט · קרגו.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ הובלות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מורט – מהנדס (2,950 $)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">בגיליון המקור מופיעה גם שורה של 3,409.28 – ראה שאלות פתוחות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גרייטדור – התקנת מחיצה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice-2055.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ מהנדס ושונות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סה"כ הוצאות הפרויקט</t>
+    <t xml:space="preserve">שולם דרכנו (צ׳קים של ישר 59,825 + 58,826 = 118,651 כולל מע"מ) ובית ירושלמי החזיר לנו את הסכום - לכן לא הוצאה ולא הכנסה של הפרויקט (לפי שמואל 15/10). חשבונית מס מרוטנברג טרם התקבלה</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1085,12 +1085,12 @@
         <v>16</v>
       </c>
       <c r="B13" s="10" t="n">
-        <f aca="false">הוצאות!D24</f>
-        <v>99716</v>
+        <f aca="false">הוצאות!D28</f>
+        <v>45928.32</v>
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B13/$B$8)</f>
-        <v>0.0654145672801709</v>
+        <v>0.0301293792240485</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1098,12 +1098,12 @@
         <v>17</v>
       </c>
       <c r="B14" s="10" t="n">
-        <f aca="false">הוצאות!D32</f>
-        <v>45928.32</v>
+        <f aca="false">הוצאות!D46</f>
+        <v>24420</v>
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B14/$B$8)</f>
-        <v>0.0301293792240485</v>
+        <v>0.0160197333725959</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,12 +1111,12 @@
         <v>18</v>
       </c>
       <c r="B15" s="10" t="n">
-        <f aca="false">הוצאות!D50</f>
-        <v>24420</v>
+        <f aca="false">הוצאות!D53</f>
+        <v>11917</v>
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B15/$B$8)</f>
-        <v>0.0160197333725959</v>
+        <v>0.0078176561261763</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1124,98 +1124,92 @@
         <v>19</v>
       </c>
       <c r="B16" s="10" t="n">
-        <f aca="false">הוצאות!D57</f>
-        <v>11917</v>
+        <f aca="false">הוצאות!D58</f>
+        <v>12889</v>
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B16/$B$8)</f>
-        <v>0.0078176561261763</v>
+        <v>0.00845529661913958</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="10" t="n">
-        <f aca="false">הוצאות!D62</f>
-        <v>12889</v>
-      </c>
-      <c r="C17" s="11" t="n">
+      <c r="B17" s="12" t="n">
+        <f aca="false">SUM(B11:B16)</f>
+        <v>1110369.77</v>
+      </c>
+      <c r="C17" s="7" t="n">
         <f aca="false">IF($B$8=0,0,B17/$B$8)</f>
-        <v>0.00845529661913958</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+        <v>0.728412271105267</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="12" t="n">
-        <f aca="false">SUM(B11:B17)</f>
-        <v>1210085.77</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <f aca="false">IF($B$8=0,0,B18/$B$8)</f>
-        <v>0.793826838385438</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="B19" s="14" t="n">
+        <f aca="false">B8-B17</f>
+        <v>414000.17</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <f aca="false">IF($B$8=0,0,B19/$B$8)</f>
+        <v>0.271587728894733</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="14" t="n">
-        <f aca="false">B8-B18</f>
-        <v>314284.17</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <f aca="false">IF($B$8=0,0,B20/$B$8)</f>
-        <v>0.206173161614562</v>
-      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="B22" s="16" t="n">
+        <f aca="false">2400*600</f>
+        <v>1440000</v>
+      </c>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">2400*600</f>
-        <v>1440000</v>
-      </c>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="16" t="n">
         <f aca="false">3000*600</f>
         <v>1800000</v>
       </c>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <f aca="false">B23-B8</f>
+        <v>275630.06</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="12" t="n">
-        <f aca="false">B24-B8</f>
-        <v>275630.06</v>
-      </c>
-      <c r="C25" s="17" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
@@ -1258,13 +1252,6 @@
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
-    </row>
-    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1274,7 +1261,8 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
@@ -1282,7 +1270,6 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1311,7 +1298,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1320,7 +1307,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -1329,19 +1316,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1349,7 +1336,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>202389.83</v>
@@ -1365,7 +1352,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>83000</v>
@@ -1381,7 +1368,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>30000</v>
@@ -1397,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="22" t="n">
         <v>300000</v>
@@ -1413,7 +1400,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="22" t="n">
         <v>35580.13</v>
@@ -1429,7 +1416,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>224579.66</v>
@@ -1445,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>228575.42</v>
@@ -1461,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>95735.59</v>
@@ -1471,7 +1458,7 @@
         <v>112968</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1479,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>197390.67</v>
@@ -1495,7 +1482,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="22" t="n">
         <v>127118.64</v>
@@ -1508,7 +1495,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="12" t="n">
@@ -1554,7 +1541,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1564,22 +1551,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1597,10 +1584,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>61</v>
       </c>
       <c r="D5" s="22" t="n">
         <v>20000</v>
@@ -1613,10 +1600,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="D6" s="22" t="n">
         <v>24700</v>
@@ -1629,7 +1616,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="22" t="n">
@@ -1637,7 +1624,7 @@
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1645,17 +1632,17 @@
         <v>14</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="D8" s="22" t="n">
         <v>140000</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1663,17 +1650,17 @@
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" s="22" t="n">
         <v>141353</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1681,10 +1668,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>125758</v>
@@ -1697,7 +1684,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="22" t="n">
@@ -1711,7 +1698,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="22" t="n">
@@ -1719,12 +1706,12 @@
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1750,7 +1737,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="22" t="n">
@@ -1760,7 +1747,7 @@
         <v>10942</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1768,7 +1755,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="22" t="n">
@@ -1778,7 +1765,7 @@
         <v>28201</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1786,7 +1773,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="22" t="n">
@@ -1796,7 +1783,7 @@
         <v>68106.41</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1804,7 +1791,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="22" t="n">
@@ -1815,7 +1802,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1826,7 +1813,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
         <v>16</v>
       </c>
@@ -1836,531 +1823,518 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="22" t="n">
+        <v>12735.59</v>
+      </c>
+      <c r="E23" s="22"/>
+      <c r="F23" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="24" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="22" t="n">
+        <v>5249</v>
+      </c>
+      <c r="E24" s="22"/>
+      <c r="F24" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="25" t="n">
-        <v>99716</v>
-      </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="19" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="22" t="n">
+        <v>18823.73</v>
+      </c>
+      <c r="E25" s="22"/>
+      <c r="F25" s="23"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="C26" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="12" t="n">
-        <f aca="false">SUM(D23:D23)</f>
-        <v>99716</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="D26" s="22" t="n">
+        <v>9120</v>
+      </c>
+      <c r="E26" s="22"/>
+      <c r="F26" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="12" t="n">
+        <f aca="false">SUM(D23:D27)</f>
+        <v>45928.32</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="22" t="n">
-        <v>12735.59</v>
-      </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+      <c r="B31" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="22" t="n">
+        <v>1455</v>
+      </c>
+      <c r="E31" s="22"/>
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="22" t="n">
-        <v>5249</v>
-      </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="B32" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="22" t="n">
+        <v>1508</v>
+      </c>
+      <c r="E32" s="22"/>
+      <c r="F32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="22" t="n">
-        <v>18823.73</v>
-      </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+      <c r="B33" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="22" t="n">
+        <v>161</v>
+      </c>
+      <c r="E33" s="22"/>
+      <c r="F33" s="23"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="22" t="n">
-        <v>9120</v>
-      </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="24" t="s">
+      <c r="B34" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="12" t="n">
-        <f aca="false">SUM(D27:D31)</f>
-        <v>45928.32</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="22" t="n">
+        <v>392</v>
+      </c>
+      <c r="E34" s="22"/>
+      <c r="F34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="22" t="n">
-        <v>1455</v>
+        <v>975</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="22" t="n">
-        <v>1508</v>
+        <v>2763</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="23"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="22" t="n">
-        <v>161</v>
+        <v>1239</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="23"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="22" t="n">
-        <v>392</v>
+        <v>2000</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="23"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="22" t="n">
-        <v>975</v>
+        <v>180</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="23"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="D40" s="22" t="n">
-        <v>2763</v>
+        <v>1659</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="22" t="n">
-        <v>1239</v>
+        <v>1160</v>
       </c>
       <c r="E41" s="22"/>
-      <c r="F41" s="23"/>
+      <c r="F41" s="23" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="22" t="n">
-        <v>2000</v>
+        <v>1160</v>
       </c>
       <c r="E42" s="22"/>
-      <c r="F42" s="23"/>
+      <c r="F42" s="23" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="22" t="n">
-        <v>180</v>
+        <v>2808</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="23"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="22" t="n">
+        <v>4640</v>
+      </c>
+      <c r="E44" s="22"/>
+      <c r="F44" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="22" t="n">
-        <v>1659</v>
-      </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="22" t="n">
-        <v>1160</v>
+        <v>2320</v>
       </c>
       <c r="E45" s="22"/>
-      <c r="F45" s="23" t="s">
-        <v>106</v>
-      </c>
+      <c r="F45" s="23"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="12" t="n">
+        <f aca="false">SUM(D31:D45)</f>
+        <v>24420</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="22" t="n">
-        <v>1160</v>
-      </c>
-      <c r="E46" s="22"/>
-      <c r="F46" s="23" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="22" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E47" s="22"/>
-      <c r="F47" s="23"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="22" t="n">
-        <v>4640</v>
-      </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="23" t="s">
-        <v>109</v>
-      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="22" t="n">
-        <v>2320</v>
+        <v>7197</v>
       </c>
       <c r="E49" s="22"/>
-      <c r="F49" s="23"/>
+      <c r="F49" s="23" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="22" t="n">
+        <v>1750</v>
+      </c>
+      <c r="E50" s="22"/>
+      <c r="F50" s="23"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="22" t="n">
+        <v>2670</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="23"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="12" t="n">
-        <f aca="false">SUM(D35:D49)</f>
-        <v>24420</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
+      <c r="C52" s="9"/>
+      <c r="D52" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E52" s="22"/>
+      <c r="F52" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="12" t="n">
+        <f aca="false">SUM(D49:D52)</f>
+        <v>11917</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="22" t="n">
-        <v>7197</v>
-      </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="22" t="n">
-        <v>1750</v>
-      </c>
-      <c r="E54" s="22"/>
-      <c r="F54" s="23"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="22" t="n">
-        <v>2670</v>
-      </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="23"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="22" t="n">
-        <v>300</v>
-      </c>
-      <c r="E56" s="22"/>
+        <v>10089</v>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>2950</v>
+      </c>
       <c r="F56" s="23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="22" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="22"/>
+      <c r="F57" s="23" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="12" t="n">
-        <f aca="false">SUM(D53:D56)</f>
-        <v>11917</v>
-      </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="12" t="n">
+        <f aca="false">SUM(D56:D57)</f>
+        <v>12889</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="9" t="s">
+      <c r="A60" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="22" t="n">
-        <v>10089</v>
-      </c>
-      <c r="E60" s="22" t="n">
-        <v>2950</v>
-      </c>
-      <c r="F60" s="23" t="s">
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="27" t="n">
+        <f aca="false">D13+D20+D28+D46+D53+D58</f>
+        <v>1110369.77</v>
+      </c>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B61" s="9" t="s">
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="22" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="23" t="s">
+      <c r="B64" s="9" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="C64" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="12" t="n">
-        <f aca="false">SUM(D60:D61)</f>
-        <v>12889</v>
-      </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="26" t="s">
+      <c r="D64" s="16" t="n">
+        <v>99716</v>
+      </c>
+      <c r="E64" s="9"/>
+      <c r="F64" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="27" t="n">
-        <f aca="false">D13+D20+D24+D32+D50+D57+D62</f>
-        <v>1210085.77</v>
-      </c>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2368,10 +2342,10 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A63:F63"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
+++ b/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="142">
   <si>
     <t xml:space="preserve">פרויקט נווה יעקב – סיכום הכנסות, הוצאות ורווח</t>
   </si>
@@ -60,7 +60,10 @@
     <t xml:space="preserve">% מההכנסות</t>
   </si>
   <si>
-    <t xml:space="preserve">💰 סה"כ הכנסות (10 תקבולים)</t>
+    <t xml:space="preserve">💰 סה"כ הכנסות (10 תקבולים, לפני ניכוי במקור)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ניכוי במקור שבית ירושלמי ניכה (20/01-25/06, כולל מע"מ) - זיכוי במס של מטה, לא הוצאה</t>
   </si>
   <si>
     <t xml:space="preserve">הוצאות לפי קטגוריה</t>
@@ -108,6 +111,15 @@
     <t xml:space="preserve">⚠️ שאלות פתוחות</t>
   </si>
   <si>
+    <t xml:space="preserve">הכנסות תוקנו לפי אישור הניכוי במקור: ב-31/03, 23/04 ו-18/05 הגיליון המקורי היה גבוה מהאישור (סה"כ כ-11,285 ₪ לפני מע"מ). לבדוק מול בית ירושלמי למה שילמו פחות.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תשלומי 10/08, 20/08 ו-29/09 לא מופיעים באישור (הוא הופק ב-10/08). נרשם הנטו שנכנס לבנק. אם נוכו 3% כמו בתשלומים האחרונים, ההכנסה גבוהה בכ-13,000 ₪ לפני מע"מ, וניכוי נוסף של כ-15,300 ₪ - לבקש אישור ניכוי מעודכן לסוף השנה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ב-16/07/2026 נכנסו לבנק מטה 108,862 ₪ מבית ירושלמי (בנק מזרחי), והם לא ברשימת התקבולים של נווה יעקב. האם זה ההחזר על בידוד רוטנברג, או פרויקט אחר?</t>
+  </si>
+  <si>
     <t xml:space="preserve">מורט: בגיליון יש "סך הכל 10,089" (2,950$) ושורה נוספת של 3,409.28 (תואמת לתשלום של מטה ל-MURAT ב-05/10). כאן נספר רק 10,089, בהנחה שה-3,409.28 הוא חלק מהסכום הזה. אם זה תשלום נוסף - הרווח יורד ב-3,409.28.</t>
   </si>
   <si>
@@ -129,10 +141,10 @@
     <t xml:space="preserve">בגיליון "סיכום" של הקובץ המקורי נווה יעקב עדיין מופיע עם נתונים ישנים: הכנסות 1,104,121 / הוצאות 725,687 / רווח 378,434.</t>
   </si>
   <si>
-    <t xml:space="preserve">פרויקט נווה יעקב – הכנסות (תקבולים מהמזמין)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מזמין: רימון בדאען ע"י בית ירושלמי · הסכומים לא כוללים מע"מ (כפי שבגיליון המקור; ×1.18 = הסכום שהתקבל בפועל)</t>
+    <t xml:space="preserve">פרויקט נווה יעקב – הכנסות מבית ירושלמי, כולל ניכוי במקור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מקור: אישור ניכוי במקור של בית ירושלמי שלי (הופק 10/08/2026, תשלומים 20/01-25/06) + דוח הבנק של מטה לתשלומים מאוחרים. ההכנסה של הפרויקט = ברוטו לפני ניכוי ÷ 1.18. הניכוי במקור הוא מקדמת מס של מטה - לא הוצאה של הפרויקט.</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -141,49 +153,91 @@
     <t xml:space="preserve">תאריך</t>
   </si>
   <si>
-    <t xml:space="preserve">סכום לפני מע"מ (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כולל מע"מ (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הערות</t>
+    <t xml:space="preserve">ברוטו כולל מע"מ (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ניכוי במקור (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% ניכוי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נטו שהתקבל בבנק (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הכנסה לפני מע"מ (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לפי הגיליון המקורי (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הפרש (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מקור / הערות</t>
   </si>
   <si>
     <t xml:space="preserve">20/01/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 010300</t>
+  </si>
+  <si>
     <t xml:space="preserve">17/02/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 807335</t>
+  </si>
+  <si>
     <t xml:space="preserve">16/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 509907</t>
+  </si>
+  <si>
     <t xml:space="preserve">31/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 70010 · ⚠️ בגיליון המקורי 300,000 (=354,000 כולל מע"מ) - גבוה מהאישור</t>
+  </si>
+  <si>
     <t xml:space="preserve">23/04/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 304311 · ⚠️ בגיליון המקורי גבוה מהאישור</t>
+  </si>
+  <si>
     <t xml:space="preserve">18/05/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 811092 · ⚠️ בגיליון המקורי גבוה מהאישור</t>
+  </si>
+  <si>
     <t xml:space="preserve">25/06/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">אישור ניכוי · אסמכתא 604090</t>
+  </si>
+  <si>
     <t xml:space="preserve">10/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">✅ תואם לבנק מטה 10/08: העברת זה"ב בית ירושלמי 112,968</t>
+    <t xml:space="preserve">בנק מטה (העברת זה"ב) · ⏳ לא באישור הניכוי - הברוטו והניכוי לא ידועים; נרשם הנטו</t>
   </si>
   <si>
     <t xml:space="preserve">20/08/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">בנק מטה (בנק הפועלים) · ⏳ לא באישור הניכוי - נרשם הנטו</t>
+  </si>
+  <si>
     <t xml:space="preserve">29/09/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">סה"כ הכנסות</t>
+    <t xml:space="preserve">סה"כ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בדיקה: סה"כ באישור הניכוי</t>
   </si>
   <si>
     <t xml:space="preserve">פרויקט נווה יעקב – הוצאות לפי קטגוריה (לא כולל מע"מ)</t>
@@ -468,16 +522,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -607,7 +661,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -640,15 +694,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -696,12 +750,20 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -972,7 +1034,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1039,177 +1101,180 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">הכנסות!C15</f>
-        <v>1524369.94</v>
+        <f aca="false">הכנסות!G15</f>
+        <v>1513084.51</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="B9" s="9" t="n">
+        <f aca="false">הכנסות!D15</f>
+        <v>46129.73</v>
+      </c>
+      <c r="C9" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <f aca="false">הוצאות!D13</f>
         <v>636119</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <f aca="false">IF($B$8=0,0,B11/$B$8)</f>
-        <v>0.417299622163896</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="C12" s="11" t="n">
+        <f aca="false">IF($B$8=0,0,B12/$B$8)</f>
+        <v>0.420412075991711</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <f aca="false">הוצאות!D20</f>
         <v>379096.45</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <f aca="false">IF($B$8=0,0,B12/$B$8)</f>
-        <v>0.248690583599412</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="C13" s="11" t="n">
+        <f aca="false">IF($B$8=0,0,B13/$B$8)</f>
+        <v>0.250545456975169</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <f aca="false">הוצאות!D28</f>
         <v>45928.32</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <f aca="false">IF($B$8=0,0,B13/$B$8)</f>
-        <v>0.0301293792240485</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="C14" s="11" t="n">
+        <f aca="false">IF($B$8=0,0,B14/$B$8)</f>
+        <v>0.0303541009748358</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="9" t="n">
         <f aca="false">הוצאות!D46</f>
         <v>24420</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <f aca="false">IF($B$8=0,0,B14/$B$8)</f>
-        <v>0.0160197333725959</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="C15" s="11" t="n">
+        <f aca="false">IF($B$8=0,0,B15/$B$8)</f>
+        <v>0.0161392174981687</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="9" t="n">
         <f aca="false">הוצאות!D53</f>
         <v>11917</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <f aca="false">IF($B$8=0,0,B15/$B$8)</f>
-        <v>0.0078176561261763</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="C16" s="11" t="n">
+        <f aca="false">IF($B$8=0,0,B16/$B$8)</f>
+        <v>0.00787596457517102</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="9" t="n">
         <f aca="false">הוצאות!D58</f>
         <v>12889</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <f aca="false">IF($B$8=0,0,B16/$B$8)</f>
-        <v>0.00845529661913958</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <f aca="false">SUM(B11:B16)</f>
+      <c r="C17" s="11" t="n">
+        <f aca="false">IF($B$8=0,0,B17/$B$8)</f>
+        <v>0.008518360947334</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <f aca="false">SUM(B12:B17)</f>
         <v>1110369.77</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <f aca="false">IF($B$8=0,0,B17/$B$8)</f>
-        <v>0.728412271105267</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="14" t="n">
-        <f aca="false">B8-B17</f>
-        <v>414000.17</v>
-      </c>
-      <c r="C19" s="15" t="n">
-        <f aca="false">IF($B$8=0,0,B19/$B$8)</f>
-        <v>0.271587728894733</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="C18" s="7" t="n">
+        <f aca="false">IF($B$8=0,0,B18/$B$8)</f>
+        <v>0.733845176962389</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="B20" s="14" t="n">
+        <f aca="false">B8-B18</f>
+        <v>402714.74</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <f aca="false">IF($B$8=0,0,B20/$B$8)</f>
+        <v>0.266154823037611</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="16" t="n">
         <f aca="false">2400*600</f>
         <v>1440000</v>
       </c>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="16" t="n">
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="16" t="n">
         <f aca="false">3000*600</f>
         <v>1800000</v>
       </c>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <f aca="false">B23-B8</f>
-        <v>275630.06</v>
-      </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="B25" s="12" t="n">
+        <f aca="false">B24-B8</f>
+        <v>286915.49</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
@@ -1253,16 +1318,43 @@
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
     </row>
+    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+    </row>
+    <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+    </row>
+    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
@@ -1270,6 +1362,10 @@
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1286,232 +1382,493 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
-    </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
         <v>41</v>
       </c>
+      <c r="B4" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="22" t="n">
+      <c r="B5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>238820</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>11941</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <f aca="false">IF(D5="","",D5/C5)</f>
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <f aca="false">C5-N(D5)</f>
+        <v>226879</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <f aca="false">ROUND(C5/1.18,2)</f>
         <v>202389.83</v>
       </c>
-      <c r="D5" s="16" t="n">
-        <f aca="false">ROUND(C5*1.18,2)</f>
-        <v>238820</v>
-      </c>
-      <c r="E5" s="9"/>
+      <c r="H5" s="23" t="n">
+        <v>202389.83</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <f aca="false">G5-H5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="22" t="n">
+      <c r="B6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>97940</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>4897</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <f aca="false">IF(D6="","",D6/C6)</f>
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <f aca="false">C6-N(D6)</f>
+        <v>93043</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <f aca="false">ROUND(C6/1.18,2)</f>
         <v>83000</v>
       </c>
-      <c r="D6" s="16" t="n">
-        <f aca="false">ROUND(C6*1.18,2)</f>
-        <v>97940</v>
-      </c>
-      <c r="E6" s="9"/>
+      <c r="H6" s="23" t="n">
+        <v>83000</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <f aca="false">G6-H6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="22" t="n">
+      <c r="B7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>35400</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>1770</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <f aca="false">IF(D7="","",D7/C7)</f>
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <f aca="false">C7-N(D7)</f>
+        <v>33630</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <f aca="false">ROUND(C7/1.18,2)</f>
         <v>30000</v>
       </c>
-      <c r="D7" s="16" t="n">
-        <f aca="false">ROUND(C7*1.18,2)</f>
-        <v>35400</v>
-      </c>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="H7" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <f aca="false">G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="22" t="n">
+      <c r="B8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>346701.03</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>10401.03</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <f aca="false">IF(D8="","",D8/C8)</f>
+        <v>0.0299999974041035</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <f aca="false">C8-N(D8)</f>
+        <v>336300</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <f aca="false">ROUND(C8/1.18,2)</f>
+        <v>293814.43</v>
+      </c>
+      <c r="H8" s="23" t="n">
         <v>300000</v>
       </c>
-      <c r="D8" s="16" t="n">
-        <f aca="false">ROUND(C8*1.18,2)</f>
-        <v>354000</v>
-      </c>
-      <c r="E8" s="9"/>
+      <c r="I8" s="16" t="n">
+        <f aca="false">G8-H8</f>
+        <v>-6185.57000000001</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="22" t="n">
+      <c r="B9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>41430.93</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>1242.93</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <f aca="false">IF(D9="","",D9/C9)</f>
+        <v>0.0300000506867695</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">C9-N(D9)</f>
+        <v>40188</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">ROUND(C9/1.18,2)</f>
+        <v>35110.96</v>
+      </c>
+      <c r="H9" s="23" t="n">
         <v>35580.13</v>
       </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">ROUND(C9*1.18,2)</f>
-        <v>41984.55</v>
-      </c>
-      <c r="E9" s="9"/>
+      <c r="I9" s="16" t="n">
+        <f aca="false">G9-H9</f>
+        <v>-469.169999999998</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="22" t="n">
+      <c r="B10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>259540.21</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>7786.21</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <f aca="false">IF(D10="","",D10/C10)</f>
+        <v>0.0300000142559798</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <f aca="false">C10-N(D10)</f>
+        <v>251754</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <f aca="false">ROUND(C10/1.18,2)</f>
+        <v>219949.33</v>
+      </c>
+      <c r="H10" s="23" t="n">
         <v>224579.66</v>
       </c>
-      <c r="D10" s="16" t="n">
-        <f aca="false">ROUND(C10*1.18,2)</f>
-        <v>265004</v>
-      </c>
-      <c r="E10" s="9"/>
+      <c r="I10" s="16" t="n">
+        <f aca="false">G10-H10</f>
+        <v>-4630.33000000002</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="22" t="n">
+      <c r="B11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>269718.56</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>8091.56</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <f aca="false">IF(D11="","",D11/C11)</f>
+        <v>0.0300000118642188</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">C11-N(D11)</f>
+        <v>261627</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">ROUND(C11/1.18,2)</f>
+        <v>228575.05</v>
+      </c>
+      <c r="H11" s="23" t="n">
         <v>228575.42</v>
       </c>
-      <c r="D11" s="16" t="n">
-        <f aca="false">ROUND(C11*1.18,2)</f>
-        <v>269719</v>
-      </c>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
+      <c r="I11" s="16" t="n">
+        <f aca="false">G11-H11</f>
+        <v>-0.370000000024447</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="22" t="n">
+      <c r="B12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>112968</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="11" t="str">
+        <f aca="false">IF(D12="","",D12/C12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">C12-N(D12)</f>
+        <v>112968</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">ROUND(C12/1.18,2)</f>
         <v>95735.59</v>
       </c>
-      <c r="D12" s="16" t="n">
-        <f aca="false">ROUND(C12*1.18,2)</f>
-        <v>112968</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>50</v>
+      <c r="H12" s="23" t="n">
+        <v>95735.59</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <f aca="false">G12-H12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="22" t="n">
+      <c r="B13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>232921</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="11" t="str">
+        <f aca="false">IF(D13="","",D13/C13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">C13-N(D13)</f>
+        <v>232921</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">ROUND(C13/1.18,2)</f>
+        <v>197390.68</v>
+      </c>
+      <c r="H13" s="23" t="n">
         <v>197390.67</v>
       </c>
-      <c r="D13" s="16" t="n">
-        <f aca="false">ROUND(C13*1.18,2)</f>
-        <v>232920.99</v>
-      </c>
-      <c r="E13" s="9"/>
+      <c r="I13" s="16" t="n">
+        <f aca="false">G13-H13</f>
+        <v>0.0099999999802094</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="22" t="n">
+      <c r="B14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="11" t="str">
+        <f aca="false">IF(D14="","",D14/C14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="16" t="n">
+        <f aca="false">C14-N(D14)</f>
+        <v>150000</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">ROUND(C14/1.18,2)</f>
         <v>127118.64</v>
       </c>
-      <c r="D14" s="16" t="n">
-        <f aca="false">ROUND(C14*1.18,2)</f>
-        <v>150000</v>
-      </c>
-      <c r="E14" s="9"/>
+      <c r="H14" s="23" t="n">
+        <v>127118.64</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <f aca="false">G14-H14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="12" t="n">
         <f aca="false">SUM(C5:C14)</f>
-        <v>1524369.94</v>
+        <v>1785439.73</v>
       </c>
       <c r="D15" s="12" t="n">
         <f aca="false">SUM(D5:D14)</f>
-        <v>1798756.54</v>
-      </c>
-      <c r="E15" s="5"/>
+        <v>46129.73</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <f aca="false">D15/SUM(C5:C11)</f>
+        <v>0.0357719389604781</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <f aca="false">SUM(F5:F14)</f>
+        <v>1739310</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <f aca="false">SUM(G5:G14)</f>
+        <v>1513084.51</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <f aca="false">SUM(H5:H14)</f>
+        <v>1524369.94</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <f aca="false">SUM(I5:I14)</f>
+        <v>-11285.4300000001</v>
+      </c>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="25" t="n">
+        <v>1289550.73</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>46129.73</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="str">
+        <f aca="false">IF(AND(ROUND(SUM(C5:C11)-C16,2)=0,ROUND(SUM(D5:D11)-D16,2)=0),"✅ תואם לאישור","❌ לא תואם")</f>
+        <v>✅ תואם לאישור</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1541,7 +1898,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1551,167 +1908,167 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="22" t="n">
+      <c r="A5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="23" t="n">
         <v>20000</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="22" t="n">
+      <c r="A6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="23" t="n">
         <v>24700</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="22" t="n">
+      <c r="A7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="23" t="n">
         <v>95000</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="23" t="s">
-        <v>64</v>
+      <c r="E7" s="23"/>
+      <c r="F7" s="24" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="22" t="n">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="23" t="n">
         <v>140000</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23" t="s">
-        <v>67</v>
+      <c r="E8" s="23"/>
+      <c r="F8" s="24" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="22" t="n">
+      <c r="A9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="23" t="n">
         <v>141353</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23" t="s">
-        <v>69</v>
+      <c r="E9" s="23"/>
+      <c r="F9" s="24" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="22" t="n">
+      <c r="A10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="23" t="n">
         <v>125758</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="22" t="n">
+      <c r="A11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="23" t="n">
         <v>87308</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="22" t="n">
+      <c r="A12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="23" t="n">
         <v>2000</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23" t="s">
-        <v>73</v>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1723,86 +2080,86 @@
       <c r="F13" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="22" t="n">
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="23" t="n">
         <v>39063</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <v>10942</v>
       </c>
-      <c r="F16" s="23" t="s">
-        <v>76</v>
+      <c r="F16" s="24" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="22" t="n">
+      <c r="A17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="23" t="n">
         <v>99831</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="23" t="n">
         <v>28201</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>78</v>
+      <c r="F17" s="24" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="22" t="n">
+      <c r="A18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="23" t="n">
         <v>235648</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="23" t="n">
         <v>68106.41</v>
       </c>
-      <c r="F18" s="23" t="s">
-        <v>80</v>
+      <c r="F18" s="24" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="22" t="n">
+      <c r="A19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="23" t="n">
         <v>4554.45</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1814,96 +2171,96 @@
       <c r="F20" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="22" t="n">
+      <c r="A23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="23" t="n">
         <v>12735.59</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="23" t="s">
-        <v>84</v>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="22" t="n">
+      <c r="A24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="23" t="n">
         <v>5249</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="23" t="s">
-        <v>85</v>
+      <c r="E24" s="23"/>
+      <c r="F24" s="24" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="22" t="n">
+      <c r="A25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="23" t="n">
         <v>18823.73</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="22" t="n">
+      <c r="A26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="23" t="n">
         <v>9120</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23" t="s">
-        <v>88</v>
+      <c r="E26" s="23"/>
+      <c r="F26" s="24" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
+      <c r="A27" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
       <c r="F27" s="19" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1915,236 +2272,236 @@
       <c r="F28" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="A30" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="22" t="n">
+      <c r="A31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="23" t="n">
         <v>1455</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="24"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="22" t="n">
+      <c r="A32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="23" t="n">
         <v>1508</v>
       </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="24"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="22" t="n">
+      <c r="A33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="23" t="n">
         <v>161</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="22" t="n">
+      <c r="A34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="23" t="n">
         <v>392</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="22" t="n">
+      <c r="A35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="23" t="n">
         <v>975</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="22" t="n">
+      <c r="A36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="23" t="n">
         <v>2763</v>
       </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="22" t="n">
+      <c r="A37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="23" t="n">
         <v>1239</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="22" t="n">
+      <c r="A38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="23" t="n">
         <v>2000</v>
       </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="22" t="n">
+      <c r="A39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="22" t="n">
+      <c r="A40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" s="23" t="n">
         <v>1659</v>
       </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="22" t="n">
+      <c r="A41" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="E41" s="22"/>
-      <c r="F41" s="23" t="s">
-        <v>101</v>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="22" t="n">
+      <c r="A42" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="23" t="n">
         <v>1160</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="23" t="s">
-        <v>102</v>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="22" t="n">
+      <c r="A43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="23" t="n">
         <v>2808</v>
       </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="22" t="n">
+      <c r="A44" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="23" t="n">
         <v>4640</v>
       </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23" t="s">
-        <v>104</v>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="22" t="n">
+      <c r="A45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="8"/>
+      <c r="D45" s="23" t="n">
         <v>2320</v>
       </c>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="24"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2156,78 +2513,78 @@
       <c r="F46" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="A48" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="22" t="n">
+      <c r="A49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="23" t="n">
         <v>7197</v>
       </c>
-      <c r="E49" s="22"/>
-      <c r="F49" s="23" t="s">
-        <v>107</v>
+      <c r="E49" s="23"/>
+      <c r="F49" s="24" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="22" t="n">
+      <c r="A50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="23" t="n">
         <v>1750</v>
       </c>
-      <c r="E50" s="22"/>
-      <c r="F50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="24"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="22" t="n">
+      <c r="A51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="23" t="n">
         <v>2670</v>
       </c>
-      <c r="E51" s="22"/>
-      <c r="F51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="24"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="22" t="n">
+      <c r="A52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="E52" s="22"/>
-      <c r="F52" s="23" t="s">
-        <v>111</v>
+      <c r="E52" s="23"/>
+      <c r="F52" s="24" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2239,52 +2596,52 @@
       <c r="F53" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="A55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="22" t="n">
+      <c r="A56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="23" t="n">
         <v>10089</v>
       </c>
-      <c r="E56" s="22" t="n">
+      <c r="E56" s="23" t="n">
         <v>2950</v>
       </c>
-      <c r="F56" s="23" t="s">
-        <v>114</v>
+      <c r="F56" s="24" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="22" t="n">
+      <c r="A57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="8"/>
+      <c r="D57" s="23" t="n">
         <v>2800</v>
       </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="23" t="s">
-        <v>116</v>
+      <c r="E57" s="23"/>
+      <c r="F57" s="24" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2296,44 +2653,44 @@
       <c r="F58" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="27" t="n">
+      <c r="A60" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="29" t="n">
         <f aca="false">D13+D20+D28+D46+D53+D58</f>
         <v>1110369.77</v>
       </c>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
+      <c r="A63" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>122</v>
+      <c r="A64" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="D64" s="16" t="n">
         <v>99716</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="23" t="s">
-        <v>123</v>
+      <c r="E64" s="8"/>
+      <c r="F64" s="24" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
+++ b/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="145">
   <si>
     <t xml:space="preserve">פרויקט נווה יעקב – סיכום הכנסות, הוצאות ורווח</t>
   </si>
@@ -60,10 +60,10 @@
     <t xml:space="preserve">% מההכנסות</t>
   </si>
   <si>
-    <t xml:space="preserve">💰 סה"כ הכנסות (10 תקבולים, לפני ניכוי במקור)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ניכוי במקור שבית ירושלמי ניכה (20/01-25/06, כולל מע"מ) - זיכוי במס של מטה, לא הוצאה</t>
+    <t xml:space="preserve">💰 סה"כ הכנסות (11 תקבולים, כולל ניכוי במקור, ללא מע"מ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   מזה ניכוי במקור שבית ירושלמי ניכה (7 באישור + 4 משוערים 3%) - זיכוי במס של מטה, לא הוצאה</t>
   </si>
   <si>
     <t xml:space="preserve">הוצאות לפי קטגוריה</t>
@@ -114,10 +114,10 @@
     <t xml:space="preserve">הכנסות תוקנו לפי אישור הניכוי במקור: ב-31/03, 23/04 ו-18/05 הגיליון המקורי היה גבוה מהאישור (סה"כ כ-11,285 ₪ לפני מע"מ). לבדוק מול בית ירושלמי למה שילמו פחות.</t>
   </si>
   <si>
-    <t xml:space="preserve">תשלומי 10/08, 20/08 ו-29/09 לא מופיעים באישור (הוא הופק ב-10/08). נרשם הנטו שנכנס לבנק. אם נוכו 3% כמו בתשלומים האחרונים, ההכנסה גבוהה בכ-13,000 ₪ לפני מע"מ, וניכוי נוסף של כ-15,300 ₪ - לבקש אישור ניכוי מעודכן לסוף השנה.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ב-16/07/2026 נכנסו לבנק מטה 108,862 ₪ מבית ירושלמי (בנק מזרחי), והם לא ברשימת התקבולים של נווה יעקב. האם זה ההחזר על בידוד רוטנברג, או פרויקט אחר?</t>
+    <t xml:space="preserve">תשלומי 16/07, 10/08, 20/08 ו-29/09 לא מופיעים באישור הניכוי (הופק 10/08) - הברוטו חושב לפי ניכוי 3% (תא E3 בגיליון "הכנסות"). לבקש מבית ירושלמי אישור ניכוי מעודכן ולעדכן לפי הסכום האמיתי.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/07/2026 - 108,862 ₪ מבית ירושלמי (בנק מזרחי) נוסף לרשימת ההכנסות - לא היה בגיליון המקורי.</t>
   </si>
   <si>
     <t xml:space="preserve">מורט: בגיליון יש "סך הכל 10,089" (2,950$) ושורה נוספת של 3,409.28 (תואמת לתשלום של מטה ל-MURAT ב-05/10). כאן נספר רק 10,089, בהנחה שה-3,409.28 הוא חלק מהסכום הזה. אם זה תשלום נוסף - הרווח יורד ב-3,409.28.</t>
@@ -144,7 +144,10 @@
     <t xml:space="preserve">פרויקט נווה יעקב – הכנסות מבית ירושלמי, כולל ניכוי במקור</t>
   </si>
   <si>
-    <t xml:space="preserve">מקור: אישור ניכוי במקור של בית ירושלמי שלי (הופק 10/08/2026, תשלומים 20/01-25/06) + דוח הבנק של מטה לתשלומים מאוחרים. ההכנסה של הפרויקט = ברוטו לפני ניכוי ÷ 1.18. הניכוי במקור הוא מקדמת מס של מטה - לא הוצאה של הפרויקט.</t>
+    <t xml:space="preserve">ההכנסה נרשמת כולל ניכוי במקור ולא כולל מע"מ (ברוטו ÷ 1.18). מקור: אישור ניכוי במקור של בית ירושלמי שלי (הופק 10/08/2026, תשלומים 20/01-25/06) + דוח הבנק של מטה לתשלומים מאוחרים. ההכנסה של הפרויקט = ברוטו לפני ניכוי ÷ 1.18. הניכוי במקור הוא מקדמת מס של מטה - לא הוצאה של הפרויקט.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% ניכוי במקור משוער לתשלומים שאינם באישור (לפי 23/04-25/06):</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -219,16 +222,22 @@
     <t xml:space="preserve">אישור ניכוי · אסמכתא 604090</t>
   </si>
   <si>
+    <t xml:space="preserve">16/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בנק מטה (בנק מזרחי) · ✅ נוסף 15/10 - לא היה ברשימה המקורית · ⏳ לא באישור הניכוי - ברוטו מחושב לפי ניכוי 3%</t>
+  </si>
+  <si>
     <t xml:space="preserve">10/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">בנק מטה (העברת זה"ב) · ⏳ לא באישור הניכוי - הברוטו והניכוי לא ידועים; נרשם הנטו</t>
+    <t xml:space="preserve">בנק מטה (העברת זה"ב) · ⏳ לא באישור הניכוי - ברוטו מחושב לפי ניכוי 3%. בגיליון המקורי נרשם הנטו בלי הניכוי</t>
   </si>
   <si>
     <t xml:space="preserve">20/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">בנק מטה (בנק הפועלים) · ⏳ לא באישור הניכוי - נרשם הנטו</t>
+    <t xml:space="preserve">בנק מטה (בנק הפועלים) · ⏳ לא באישור הניכוי - ברוטו מחושב לפי ניכוי 3%. בגיליון המקורי נרשם הנטו בלי הניכוי</t>
   </si>
   <si>
     <t xml:space="preserve">29/09/2026</t>
@@ -459,7 +468,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,6 +570,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -661,7 +678,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -750,11 +767,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -762,7 +787,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -770,11 +795,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1101,8 +1122,8 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">הכנסות!G15</f>
-        <v>1513084.51</v>
+        <f aca="false">הכנסות!G16</f>
+        <v>1621190.99</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">1</f>
@@ -1114,8 +1135,8 @@
         <v>13</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">הכנסות!D15</f>
-        <v>46129.73</v>
+        <f aca="false">הכנסות!D16</f>
+        <v>64833.38</v>
       </c>
       <c r="C9" s="8"/>
     </row>
@@ -1136,7 +1157,7 @@
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B12/$B$8)</f>
-        <v>0.420412075991711</v>
+        <v>0.392377581619794</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1149,7 +1170,7 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B13/$B$8)</f>
-        <v>0.250545456975169</v>
+        <v>0.233838241353661</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1162,7 +1183,7 @@
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B14/$B$8)</f>
-        <v>0.0303541009748358</v>
+        <v>0.0283299872028033</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1175,7 +1196,7 @@
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B15/$B$8)</f>
-        <v>0.0161392174981687</v>
+        <v>0.0150630000725578</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1188,7 +1209,7 @@
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B16/$B$8)</f>
-        <v>0.00787596457517102</v>
+        <v>0.00735076870862698</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1201,7 +1222,7 @@
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B17/$B$8)</f>
-        <v>0.008518360947334</v>
+        <v>0.00795032792527425</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,7 +1235,7 @@
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">IF($B$8=0,0,B18/$B$8)</f>
-        <v>0.733845176962389</v>
+        <v>0.684909906882717</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1223,11 +1244,11 @@
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">B8-B18</f>
-        <v>402714.74</v>
+        <v>510821.22</v>
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">IF($B$8=0,0,B20/$B$8)</f>
-        <v>0.266154823037611</v>
+        <v>0.315090093117283</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1263,7 +1284,7 @@
       </c>
       <c r="B25" s="12" t="n">
         <f aca="false">B24-B8</f>
-        <v>286915.49</v>
+        <v>178809.01</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>27</v>
@@ -1276,70 +1297,70 @@
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
     </row>
-    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
         <v>29</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
     </row>
-    <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
     </row>
-    <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
         <v>31</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
     </row>
-    <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
     </row>
-    <row r="32" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
     </row>
-    <row r="33" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
     </row>
-    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
     </row>
-    <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
     </row>
-    <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
     </row>
-    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
         <v>38</v>
       </c>
@@ -1382,7 +1403,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1423,36 +1444,47 @@
       <c r="I2" s="21"/>
       <c r="J2" s="21"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="23" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="C4" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="D4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="F4" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="G4" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="H4" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="I4" s="24" t="s">
         <v>50</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1460,35 +1492,35 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="23" t="n">
+        <v>52</v>
+      </c>
+      <c r="C5" s="25" t="n">
         <v>238820</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="25" t="n">
         <v>11941</v>
       </c>
       <c r="E5" s="11" t="n">
-        <f aca="false">IF(D5="","",D5/C5)</f>
+        <f aca="false">D5/C5</f>
         <v>0.05</v>
       </c>
       <c r="F5" s="16" t="n">
-        <f aca="false">C5-N(D5)</f>
+        <f aca="false">C5-D5</f>
         <v>226879</v>
       </c>
       <c r="G5" s="16" t="n">
         <f aca="false">ROUND(C5/1.18,2)</f>
         <v>202389.83</v>
       </c>
-      <c r="H5" s="23" t="n">
+      <c r="H5" s="25" t="n">
         <v>202389.83</v>
       </c>
       <c r="I5" s="16" t="n">
-        <f aca="false">G5-H5</f>
+        <f aca="false">G5-N(H5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="24" t="s">
-        <v>52</v>
+      <c r="J5" s="26" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1496,35 +1528,35 @@
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="23" t="n">
+        <v>54</v>
+      </c>
+      <c r="C6" s="25" t="n">
         <v>97940</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>4897</v>
       </c>
       <c r="E6" s="11" t="n">
-        <f aca="false">IF(D6="","",D6/C6)</f>
+        <f aca="false">D6/C6</f>
         <v>0.05</v>
       </c>
       <c r="F6" s="16" t="n">
-        <f aca="false">C6-N(D6)</f>
+        <f aca="false">C6-D6</f>
         <v>93043</v>
       </c>
       <c r="G6" s="16" t="n">
         <f aca="false">ROUND(C6/1.18,2)</f>
         <v>83000</v>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="H6" s="25" t="n">
         <v>83000</v>
       </c>
       <c r="I6" s="16" t="n">
-        <f aca="false">G6-H6</f>
+        <f aca="false">G6-N(H6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="24" t="s">
-        <v>54</v>
+      <c r="J6" s="26" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1532,35 +1564,35 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="23" t="n">
+        <v>56</v>
+      </c>
+      <c r="C7" s="25" t="n">
         <v>35400</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="25" t="n">
         <v>1770</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">IF(D7="","",D7/C7)</f>
+        <f aca="false">D7/C7</f>
         <v>0.05</v>
       </c>
       <c r="F7" s="16" t="n">
-        <f aca="false">C7-N(D7)</f>
+        <f aca="false">C7-D7</f>
         <v>33630</v>
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">ROUND(C7/1.18,2)</f>
         <v>30000</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="H7" s="25" t="n">
         <v>30000</v>
       </c>
       <c r="I7" s="16" t="n">
-        <f aca="false">G7-H7</f>
+        <f aca="false">G7-N(H7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="24" t="s">
-        <v>56</v>
+      <c r="J7" s="26" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1568,35 +1600,35 @@
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="23" t="n">
+        <v>58</v>
+      </c>
+      <c r="C8" s="25" t="n">
         <v>346701.03</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="25" t="n">
         <v>10401.03</v>
       </c>
       <c r="E8" s="11" t="n">
-        <f aca="false">IF(D8="","",D8/C8)</f>
+        <f aca="false">D8/C8</f>
         <v>0.0299999974041035</v>
       </c>
       <c r="F8" s="16" t="n">
-        <f aca="false">C8-N(D8)</f>
+        <f aca="false">C8-D8</f>
         <v>336300</v>
       </c>
       <c r="G8" s="16" t="n">
         <f aca="false">ROUND(C8/1.18,2)</f>
         <v>293814.43</v>
       </c>
-      <c r="H8" s="23" t="n">
+      <c r="H8" s="25" t="n">
         <v>300000</v>
       </c>
       <c r="I8" s="16" t="n">
-        <f aca="false">G8-H8</f>
+        <f aca="false">G8-N(H8)</f>
         <v>-6185.57000000001</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,35 +1636,35 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <v>41430.93</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>1242.93</v>
       </c>
       <c r="E9" s="11" t="n">
-        <f aca="false">IF(D9="","",D9/C9)</f>
+        <f aca="false">D9/C9</f>
         <v>0.0300000506867695</v>
       </c>
       <c r="F9" s="16" t="n">
-        <f aca="false">C9-N(D9)</f>
+        <f aca="false">C9-D9</f>
         <v>40188</v>
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">ROUND(C9/1.18,2)</f>
         <v>35110.96</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H9" s="25" t="n">
         <v>35580.13</v>
       </c>
       <c r="I9" s="16" t="n">
-        <f aca="false">G9-H9</f>
+        <f aca="false">G9-N(H9)</f>
         <v>-469.169999999998</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1640,35 +1672,35 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="23" t="n">
+        <v>62</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <v>259540.21</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="25" t="n">
         <v>7786.21</v>
       </c>
       <c r="E10" s="11" t="n">
-        <f aca="false">IF(D10="","",D10/C10)</f>
+        <f aca="false">D10/C10</f>
         <v>0.0300000142559798</v>
       </c>
       <c r="F10" s="16" t="n">
-        <f aca="false">C10-N(D10)</f>
+        <f aca="false">C10-D10</f>
         <v>251754</v>
       </c>
       <c r="G10" s="16" t="n">
         <f aca="false">ROUND(C10/1.18,2)</f>
         <v>219949.33</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="25" t="n">
         <v>224579.66</v>
       </c>
       <c r="I10" s="16" t="n">
-        <f aca="false">G10-H10</f>
+        <f aca="false">G10-N(H10)</f>
         <v>-4630.33000000002</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1676,35 +1708,35 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="23" t="n">
+        <v>64</v>
+      </c>
+      <c r="C11" s="25" t="n">
         <v>269718.56</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="25" t="n">
         <v>8091.56</v>
       </c>
       <c r="E11" s="11" t="n">
-        <f aca="false">IF(D11="","",D11/C11)</f>
+        <f aca="false">D11/C11</f>
         <v>0.0300000118642188</v>
       </c>
       <c r="F11" s="16" t="n">
-        <f aca="false">C11-N(D11)</f>
+        <f aca="false">C11-D11</f>
         <v>261627</v>
       </c>
       <c r="G11" s="16" t="n">
         <f aca="false">ROUND(C11/1.18,2)</f>
         <v>228575.05</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="25" t="n">
         <v>228575.42</v>
       </c>
       <c r="I11" s="16" t="n">
-        <f aca="false">G11-H11</f>
+        <f aca="false">G11-N(H11)</f>
         <v>-0.370000000024447</v>
       </c>
-      <c r="J11" s="24" t="s">
-        <v>64</v>
+      <c r="J11" s="26" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1712,163 +1744,208 @@
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>112968</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="11" t="str">
-        <f aca="false">IF(D12="","",D12/C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="16" t="n">
-        <f aca="false">C12-N(D12)</f>
-        <v>112968</v>
+        <v>66</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">ROUND(F12/(1-$E$3),2)</f>
+        <v>112228.87</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">C12-F12</f>
+        <v>3366.87</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <f aca="false">D12/C12</f>
+        <v>0.0300000347504167</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>108862</v>
       </c>
       <c r="G12" s="16" t="n">
         <f aca="false">ROUND(C12/1.18,2)</f>
-        <v>95735.59</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>95735.59</v>
-      </c>
+        <v>95109.21</v>
+      </c>
+      <c r="H12" s="25"/>
       <c r="I12" s="16" t="n">
-        <f aca="false">G12-H12</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">G12-N(H12)</f>
+        <v>95109.21</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="23" t="n">
-        <v>232921</v>
-      </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="11" t="str">
-        <f aca="false">IF(D13="","",D13/C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16" t="n">
-        <f aca="false">C13-N(D13)</f>
-        <v>232921</v>
+        <v>68</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">ROUND(F13/(1-$E$3),2)</f>
+        <v>116461.86</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">C13-F13</f>
+        <v>3493.86</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <f aca="false">D13/C13</f>
+        <v>0.0300000360633086</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>112968</v>
       </c>
       <c r="G13" s="16" t="n">
         <f aca="false">ROUND(C13/1.18,2)</f>
-        <v>197390.68</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>197390.67</v>
+        <v>98696.49</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>95735.59</v>
       </c>
       <c r="I13" s="16" t="n">
-        <f aca="false">G13-H13</f>
-        <v>0.0099999999802094</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">G13-N(H13)</f>
+        <v>2960.90000000001</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="11" t="str">
-        <f aca="false">IF(D14="","",D14/C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="16" t="n">
-        <f aca="false">C14-N(D14)</f>
-        <v>150000</v>
+        <v>70</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">ROUND(F14/(1-$E$3),2)</f>
+        <v>240124.74</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">C14-F14</f>
+        <v>7203.73999999999</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <f aca="false">D14/C14</f>
+        <v>0.0299999908380952</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>232921</v>
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">ROUND(C14/1.18,2)</f>
+        <v>203495.54</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>197390.67</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <f aca="false">G14-N(H14)</f>
+        <v>6104.87</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">ROUND(F15/(1-$E$3),2)</f>
+        <v>154639.18</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">C15-F15</f>
+        <v>4639.17999999999</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <f aca="false">D15/C15</f>
+        <v>0.0300000297466657</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <f aca="false">ROUND(C15/1.18,2)</f>
+        <v>131050.15</v>
+      </c>
+      <c r="H15" s="25" t="n">
         <v>127118.64</v>
       </c>
-      <c r="H14" s="23" t="n">
-        <v>127118.64</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <f aca="false">G14-H14</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="12" t="n">
-        <f aca="false">SUM(C5:C14)</f>
-        <v>1785439.73</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <f aca="false">SUM(D5:D14)</f>
+      <c r="I15" s="16" t="n">
+        <f aca="false">G15-N(H15)</f>
+        <v>3931.50999999999</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="12" t="n">
+        <f aca="false">SUM(C5:C15)</f>
+        <v>1913005.38</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <f aca="false">SUM(D5:D15)</f>
+        <v>64833.38</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <f aca="false">D16/SUM(C5:C11)</f>
+        <v>0.0502759437777217</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <f aca="false">SUM(F5:F15)</f>
+        <v>1848172</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <f aca="false">SUM(G5:G15)</f>
+        <v>1621190.99</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <f aca="false">SUM(H5:H15)</f>
+        <v>1524369.94</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <f aca="false">SUM(I5:I15)</f>
+        <v>96821.05</v>
+      </c>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="27" t="n">
+        <v>1289550.73</v>
+      </c>
+      <c r="D17" s="27" t="n">
         <v>46129.73</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <f aca="false">D15/SUM(C5:C11)</f>
-        <v>0.0357719389604781</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <f aca="false">SUM(F5:F14)</f>
-        <v>1739310</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <f aca="false">SUM(G5:G14)</f>
-        <v>1513084.51</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <f aca="false">SUM(H5:H14)</f>
-        <v>1524369.94</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <f aca="false">SUM(I5:I14)</f>
-        <v>-11285.4300000001</v>
-      </c>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="25" t="n">
-        <v>1289550.73</v>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>46129.73</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="str">
-        <f aca="false">IF(AND(ROUND(SUM(C5:C11)-C16,2)=0,ROUND(SUM(D5:D11)-D16,2)=0),"✅ תואם לאישור","❌ לא תואם")</f>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="str">
+        <f aca="false">IF(AND(ROUND(SUM(C5:C11)-C17,2)=0,ROUND(SUM(D5:D11)-D17,2)=0),"✅ תואם לאישור","❌ לא תואם")</f>
         <v>✅ תואם לאישור</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1898,7 +1975,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1908,22 +1985,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1941,47 +2018,47 @@
         <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="D5" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="D6" s="25" t="n">
         <v>24700</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="25" t="n">
         <v>95000</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24" t="s">
-        <v>82</v>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1989,17 +2066,17 @@
         <v>15</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="D8" s="25" t="n">
         <v>140000</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24" t="s">
-        <v>85</v>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2007,17 +2084,17 @@
         <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="D9" s="25" t="n">
         <v>141353</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24" t="s">
-        <v>87</v>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2025,50 +2102,50 @@
         <v>15</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="23" t="n">
+        <v>92</v>
+      </c>
+      <c r="D10" s="25" t="n">
         <v>125758</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="25" t="n">
         <v>87308</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="25" t="n">
         <v>2000</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24" t="s">
-        <v>91</v>
+      <c r="E12" s="25"/>
+      <c r="F12" s="26" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2094,17 +2171,17 @@
         <v>16</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="25" t="n">
         <v>39063</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="25" t="n">
         <v>10942</v>
       </c>
-      <c r="F16" s="24" t="s">
-        <v>94</v>
+      <c r="F16" s="26" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2112,17 +2189,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="25" t="n">
         <v>99831</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="25" t="n">
         <v>28201</v>
       </c>
-      <c r="F17" s="24" t="s">
-        <v>96</v>
+      <c r="F17" s="26" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2130,17 +2207,17 @@
         <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="25" t="n">
         <v>235648</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="25" t="n">
         <v>68106.41</v>
       </c>
-      <c r="F18" s="24" t="s">
-        <v>98</v>
+      <c r="F18" s="26" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2148,18 +2225,18 @@
         <v>16</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C19" s="8"/>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="25" t="n">
         <v>4554.45</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2185,15 +2262,15 @@
         <v>17</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" s="8"/>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="25" t="n">
         <v>12735.59</v>
       </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="24" t="s">
-        <v>102</v>
+      <c r="E23" s="25"/>
+      <c r="F23" s="26" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,15 +2278,15 @@
         <v>17</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C24" s="8"/>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="25" t="n">
         <v>5249</v>
       </c>
-      <c r="E24" s="23"/>
-      <c r="F24" s="24" t="s">
-        <v>103</v>
+      <c r="E24" s="25"/>
+      <c r="F24" s="26" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2217,50 +2294,50 @@
         <v>17</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="25" t="n">
         <v>18823.73</v>
       </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="23" t="n">
+        <v>108</v>
+      </c>
+      <c r="D26" s="25" t="n">
         <v>9120</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24" t="s">
-        <v>106</v>
+      <c r="E26" s="25"/>
+      <c r="F26" s="26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
+      <c r="B27" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2286,157 +2363,157 @@
         <v>18</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="25" t="n">
         <v>1455</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C32" s="8"/>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="25" t="n">
         <v>1508</v>
       </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="26"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C33" s="8"/>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="25" t="n">
         <v>161</v>
       </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="25" t="n">
         <v>392</v>
       </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="24"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C35" s="8"/>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="25" t="n">
         <v>975</v>
       </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="24"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="25" t="n">
         <v>2763</v>
       </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C37" s="8"/>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="25" t="n">
         <v>1239</v>
       </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="24"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C38" s="8"/>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="25" t="n">
         <v>2000</v>
       </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="24"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="26"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C39" s="8"/>
-      <c r="D39" s="23" t="n">
+      <c r="D39" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="24"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="26"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D40" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="D40" s="25" t="n">
         <v>1659</v>
       </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="24"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C41" s="8"/>
-      <c r="D41" s="23" t="n">
+      <c r="D41" s="25" t="n">
         <v>1160</v>
       </c>
-      <c r="E41" s="23"/>
-      <c r="F41" s="24" t="s">
-        <v>119</v>
+      <c r="E41" s="25"/>
+      <c r="F41" s="26" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,15 +2521,15 @@
         <v>18</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C42" s="8"/>
-      <c r="D42" s="23" t="n">
+      <c r="D42" s="25" t="n">
         <v>1160</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="24" t="s">
-        <v>120</v>
+      <c r="E42" s="25"/>
+      <c r="F42" s="26" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2460,29 +2537,29 @@
         <v>18</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="D43" s="23" t="n">
+      <c r="D43" s="25" t="n">
         <v>2808</v>
       </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="24"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="26"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C44" s="8"/>
-      <c r="D44" s="23" t="n">
+      <c r="D44" s="25" t="n">
         <v>4640</v>
       </c>
-      <c r="E44" s="23"/>
-      <c r="F44" s="24" t="s">
-        <v>122</v>
+      <c r="E44" s="25"/>
+      <c r="F44" s="26" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2490,18 +2567,18 @@
         <v>18</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C45" s="8"/>
-      <c r="D45" s="23" t="n">
+      <c r="D45" s="25" t="n">
         <v>2320</v>
       </c>
-      <c r="E45" s="23"/>
-      <c r="F45" s="24"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="26"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2527,15 +2604,15 @@
         <v>19</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="23" t="n">
+      <c r="D49" s="25" t="n">
         <v>7197</v>
       </c>
-      <c r="E49" s="23"/>
-      <c r="F49" s="24" t="s">
-        <v>125</v>
+      <c r="E49" s="25"/>
+      <c r="F49" s="26" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2543,48 +2620,48 @@
         <v>19</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C50" s="8"/>
-      <c r="D50" s="23" t="n">
+      <c r="D50" s="25" t="n">
         <v>1750</v>
       </c>
-      <c r="E50" s="23"/>
-      <c r="F50" s="24"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C51" s="8"/>
-      <c r="D51" s="23" t="n">
+      <c r="D51" s="25" t="n">
         <v>2670</v>
       </c>
-      <c r="E51" s="23"/>
-      <c r="F51" s="24"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C52" s="8"/>
-      <c r="D52" s="23" t="n">
+      <c r="D52" s="25" t="n">
         <v>300</v>
       </c>
-      <c r="E52" s="23"/>
-      <c r="F52" s="24" t="s">
-        <v>129</v>
+      <c r="E52" s="25"/>
+      <c r="F52" s="26" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2610,17 +2687,17 @@
         <v>20</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C56" s="8"/>
-      <c r="D56" s="23" t="n">
+      <c r="D56" s="25" t="n">
         <v>10089</v>
       </c>
-      <c r="E56" s="23" t="n">
+      <c r="E56" s="25" t="n">
         <v>2950</v>
       </c>
-      <c r="F56" s="24" t="s">
-        <v>132</v>
+      <c r="F56" s="26" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2628,20 +2705,20 @@
         <v>20</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C57" s="8"/>
-      <c r="D57" s="23" t="n">
+      <c r="D57" s="25" t="n">
         <v>2800</v>
       </c>
-      <c r="E57" s="23"/>
-      <c r="F57" s="24" t="s">
-        <v>134</v>
+      <c r="E57" s="25"/>
+      <c r="F57" s="26" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2653,21 +2730,21 @@
       <c r="F58" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="29" t="n">
+      <c r="A60" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="30" t="n">
         <f aca="false">D13+D20+D28+D46+D53+D58</f>
         <v>1110369.77</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -2677,20 +2754,20 @@
     </row>
     <row r="64" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D64" s="16" t="n">
         <v>99716</v>
       </c>
       <c r="E64" s="8"/>
-      <c r="F64" s="24" t="s">
-        <v>141</v>
+      <c r="F64" s="26" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
+++ b/CLUDE FILES/פרויקט נווה יעקב - הכנסות והוצאות.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="147">
   <si>
     <t xml:space="preserve">פרויקט נווה יעקב – סיכום הכנסות, הוצאות ורווח</t>
   </si>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">הובלות</t>
   </si>
   <si>
-    <t xml:space="preserve">מהנדס ושונות</t>
+    <t xml:space="preserve">מהנדס, מדידות ושונות</t>
   </si>
   <si>
     <t xml:space="preserve">📤 סה"כ הוצאות</t>
@@ -426,6 +426,12 @@
     <t xml:space="preserve">סה"כ הובלות</t>
   </si>
   <si>
+    <t xml:space="preserve">מדידות – נווה יעקב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ העברה של 5,000 ₪ (לפי שמואל 15/10). אם הסכום כולל מע"מ - לפני מע"מ 4,237.29 (לעדכן כשתגיע חשבונית)</t>
+  </si>
+  <si>
     <t xml:space="preserve">מורט – מהנדס (2,950 $)</t>
   </si>
   <si>
@@ -438,7 +444,7 @@
     <t xml:space="preserve">Invoice-2055.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">סה"כ מהנדס ושונות</t>
+    <t xml:space="preserve">סה"כ מהנדס, מדידות ושונות</t>
   </si>
   <si>
     <t xml:space="preserve">סה"כ הוצאות הפרויקט</t>
@@ -1217,12 +1223,12 @@
         <v>20</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">הוצאות!D58</f>
-        <v>12889</v>
+        <f aca="false">הוצאות!D59</f>
+        <v>17889</v>
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">IF($B$8=0,0,B17/$B$8)</f>
-        <v>0.00795032792527425</v>
+        <v>0.0110344802742828</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1231,11 +1237,11 @@
       </c>
       <c r="B18" s="12" t="n">
         <f aca="false">SUM(B12:B17)</f>
-        <v>1110369.77</v>
+        <v>1115369.77</v>
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">IF($B$8=0,0,B18/$B$8)</f>
-        <v>0.684909906882717</v>
+        <v>0.687994059231726</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1244,11 +1250,11 @@
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">B8-B18</f>
-        <v>510821.22</v>
+        <v>505821.22</v>
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">IF($B$8=0,0,B20/$B$8)</f>
-        <v>0.315090093117283</v>
+        <v>0.312005940768274</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1962,7 +1968,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -2672,7 +2678,7 @@
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
         <v>20</v>
       </c>
@@ -2682,21 +2688,19 @@
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="25" t="n">
-        <v>10089</v>
-      </c>
-      <c r="E56" s="25" t="n">
-        <v>2950</v>
-      </c>
-      <c r="F56" s="26" t="s">
+      <c r="C56" s="28"/>
+      <c r="D56" s="29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E56" s="29"/>
+      <c r="F56" s="19" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2709,65 +2713,83 @@
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="25" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E57" s="25"/>
+        <v>10089</v>
+      </c>
+      <c r="E57" s="25" t="n">
+        <v>2950</v>
+      </c>
       <c r="F57" s="26" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="12" t="n">
-        <f aca="false">SUM(D56:D57)</f>
-        <v>12889</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22" t="s">
+      <c r="C58" s="8"/>
+      <c r="D58" s="25" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="25"/>
+      <c r="F58" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="30" t="n">
-        <f aca="false">D13+D20+D28+D46+D53+D58</f>
-        <v>1110369.77</v>
-      </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-    </row>
-    <row r="64" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="8" t="s">
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="12" t="n">
+        <f aca="false">SUM(D56:D58)</f>
+        <v>17889</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="30" t="n">
+        <f aca="false">D13+D20+D28+D46+D53+D59</f>
+        <v>1115369.77</v>
+      </c>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+    </row>
+    <row r="65" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="16" t="n">
+      <c r="B65" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D65" s="16" t="n">
         <v>99716</v>
       </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="26" t="s">
-        <v>144</v>
+      <c r="E65" s="8"/>
+      <c r="F65" s="26" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2779,7 +2801,7 @@
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A64:F64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
